--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-fetal-death-record-identifier.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-fetal-death-record-identifier.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T12:23:49-04:00</t>
+    <t>2026-10-19T10:14:35-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
